--- a/examples/invoice/template.xlsx
+++ b/examples/invoice/template.xlsx
@@ -1,104 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice {{ invoice_no }}" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Invoice" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">Invoice #</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ invoice_no }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ customer }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ date }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{%tr for line in lines %}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ line.description }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ line.qty }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{ line.unit_price }}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{%tr endfor %}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtotal</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Invoice #</t>
+  </si>
+  <si>
+    <t>{{ invoice_no }}</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>{{ customer }}</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>{{ date }}</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>Line total</t>
+  </si>
+  <si>
+    <t>{%tr for line in lines %}</t>
+  </si>
+  <si>
+    <t>{{ line.description }}</t>
+  </si>
+  <si>
+    <t>{{ line.qty }}</t>
+  </si>
+  <si>
+    <t>{{ line.unit_price }}</t>
+  </si>
+  <si>
+    <t>{%tr endfor %}</t>
+  </si>
+  <si>
+    <t>{%tr if show_notes %}</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>{{ notes }}</t>
+  </si>
+  <si>
+    <t>Payment terms</t>
+  </si>
+  <si>
+    <t>{{ payment_terms }}</t>
+  </si>
+  <si>
+    <t>{%tr endif %}</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,7 +103,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -118,45 +111,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
@@ -165,93 +130,157 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -259,24 +288,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -289,7 +327,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -299,13 +343,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -313,6 +359,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -320,105 +367,121 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="0" t="e">
-        <f aca="false">{{ line.qty }}*{{ line.unit_price }}</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="D7" t="str">
+        <f>={{ line.qty }}*{{ line.unit_price }}</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+    <row r="9">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="0" t="e">
-        <f aca="false">SUM(D7:D9)</f>
-        <v>#N/A</v>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="str">
+        <f>=SUM(D7:D9)</f>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
 </worksheet>
 </file>